--- a/research/traditional_assets/database/data/thailand/thailand_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0319</v>
+        <v>-0.005899999999999997</v>
       </c>
       <c r="E2">
-        <v>-0.106</v>
+        <v>0.01235</v>
+      </c>
+      <c r="F2">
+        <v>0.0401</v>
       </c>
       <c r="G2">
-        <v>0.04087580863012725</v>
+        <v>0.1056012271409055</v>
       </c>
       <c r="H2">
-        <v>0.04087580863012725</v>
+        <v>0.1056012271409055</v>
       </c>
       <c r="I2">
-        <v>0.07268859007727439</v>
+        <v>0.08782846574038765</v>
       </c>
       <c r="J2">
-        <v>0.06177519657169658</v>
+        <v>0.07256384678990965</v>
       </c>
       <c r="K2">
-        <v>91.8</v>
+        <v>302.6</v>
       </c>
       <c r="L2">
-        <v>0.06525911708253358</v>
+        <v>0.07252594492246485</v>
       </c>
       <c r="M2">
-        <v>11.7</v>
+        <v>109.9</v>
       </c>
       <c r="N2">
-        <v>0.006134647651006711</v>
+        <v>0.01729238128205935</v>
       </c>
       <c r="O2">
-        <v>0.1274509803921569</v>
+        <v>0.3631857237276933</v>
       </c>
       <c r="P2">
-        <v>11.7</v>
+        <v>109.9</v>
       </c>
       <c r="Q2">
-        <v>0.006134647651006711</v>
+        <v>0.01729238128205935</v>
       </c>
       <c r="R2">
-        <v>0.1274509803921569</v>
+        <v>0.3631857237276933</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>272.4</v>
+        <v>420.5</v>
       </c>
       <c r="V2">
-        <v>0.1428271812080537</v>
+        <v>0.06616420681625075</v>
       </c>
       <c r="W2">
-        <v>0.06848190973517344</v>
+        <v>0.07372420106846109</v>
       </c>
       <c r="X2">
-        <v>0.07076184092187615</v>
+        <v>0.1084261854794475</v>
       </c>
       <c r="Y2">
-        <v>-0.002279931186702708</v>
+        <v>-0.03470198441098644</v>
       </c>
       <c r="Z2">
-        <v>1.336319015115338</v>
+        <v>1.184501701196897</v>
       </c>
       <c r="AA2">
-        <v>0.08255136984124596</v>
+        <v>0.08126128564177362</v>
       </c>
       <c r="AB2">
-        <v>0.07073538933421071</v>
+        <v>0.1084114472838926</v>
       </c>
       <c r="AC2">
-        <v>0.01181598050703525</v>
+        <v>-0.02715016164211895</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="AE2">
-        <v>1.224801691490527</v>
+        <v>0.8564619569033876</v>
       </c>
       <c r="AF2">
-        <v>1.224801691490527</v>
+        <v>0.8634619569033876</v>
       </c>
       <c r="AG2">
-        <v>-271.1751983085094</v>
+        <v>-419.6365380430966</v>
       </c>
       <c r="AH2">
-        <v>0.0006417867187666765</v>
+        <v>0.0001358442679525989</v>
       </c>
       <c r="AI2">
-        <v>0.0008672852155149252</v>
+        <v>0.0002484737232445098</v>
       </c>
       <c r="AJ2">
-        <v>-0.1657524983900859</v>
+        <v>-0.0706963039771721</v>
       </c>
       <c r="AK2">
-        <v>-0.2379095435597538</v>
+        <v>-0.1373801995831695</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>1.855690873712283e-05</v>
       </c>
       <c r="AP2">
-        <v>-2.553534957140659</v>
+        <v>-1.112450991318274</v>
       </c>
     </row>
     <row r="3">
@@ -707,124 +710,255 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Thai Life Insurance Public Company Limited (SET:TLI)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0284</v>
+      </c>
+      <c r="E3">
+        <v>0.0622</v>
+      </c>
+      <c r="F3">
+        <v>0.0401</v>
+      </c>
+      <c r="G3">
+        <v>0.1146292311370701</v>
+      </c>
+      <c r="H3">
+        <v>0.1146292311370701</v>
+      </c>
+      <c r="I3">
+        <v>0.09252997233323086</v>
+      </c>
+      <c r="J3">
+        <v>0.07432455511152099</v>
+      </c>
+      <c r="K3">
+        <v>217.6</v>
+      </c>
+      <c r="L3">
+        <v>0.07432455511152099</v>
+      </c>
+      <c r="M3">
+        <v>70.2</v>
+      </c>
+      <c r="N3">
+        <v>0.01422405932770044</v>
+      </c>
+      <c r="O3">
+        <v>0.3226102941176471</v>
+      </c>
+      <c r="P3">
+        <v>70.2</v>
+      </c>
+      <c r="Q3">
+        <v>0.01422405932770044</v>
+      </c>
+      <c r="R3">
+        <v>0.3226102941176471</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>150</v>
+      </c>
+      <c r="V3">
+        <v>0.03039328916175308</v>
+      </c>
+      <c r="W3">
+        <v>0.08720743828150049</v>
+      </c>
+      <c r="X3">
+        <v>0.1084094324182162</v>
+      </c>
+      <c r="Y3">
+        <v>-0.0212019941367157</v>
+      </c>
+      <c r="Z3">
+        <v>1.228525869665562</v>
+      </c>
+      <c r="AA3">
+        <v>0.09130963870588729</v>
+      </c>
+      <c r="AB3">
+        <v>0.1084093675666564</v>
+      </c>
+      <c r="AC3">
+        <v>-0.01709972886076906</v>
+      </c>
+      <c r="AD3">
+        <v>0.007</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.007</v>
+      </c>
+      <c r="AG3">
+        <v>-149.993</v>
+      </c>
+      <c r="AH3">
+        <v>1.418351482491363e-06</v>
+      </c>
+      <c r="AI3">
+        <v>2.948104516201308e-06</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.0313444884518381</v>
+      </c>
+      <c r="AK3">
+        <v>-0.06743055564921346</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>2.510760401721664e-05</v>
+      </c>
+      <c r="AP3">
+        <v>-0.5379949784791965</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Bangkok Life Assurance Public Company Limited (SET:BLA)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0319</v>
-      </c>
-      <c r="E3">
-        <v>-0.106</v>
-      </c>
-      <c r="G3">
-        <v>0.04087580863012725</v>
-      </c>
-      <c r="H3">
-        <v>0.04087580863012725</v>
-      </c>
-      <c r="I3">
-        <v>0.07268859007727439</v>
-      </c>
-      <c r="J3">
-        <v>0.06177519657169658</v>
-      </c>
-      <c r="K3">
-        <v>91.8</v>
-      </c>
-      <c r="L3">
-        <v>0.06525911708253358</v>
-      </c>
-      <c r="M3">
-        <v>11.7</v>
-      </c>
-      <c r="N3">
-        <v>0.006134647651006711</v>
-      </c>
-      <c r="O3">
-        <v>0.1274509803921569</v>
-      </c>
-      <c r="P3">
-        <v>11.7</v>
-      </c>
-      <c r="Q3">
-        <v>0.006134647651006711</v>
-      </c>
-      <c r="R3">
-        <v>0.1274509803921569</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>272.4</v>
-      </c>
-      <c r="V3">
-        <v>0.1428271812080537</v>
-      </c>
-      <c r="W3">
-        <v>0.06848190973517344</v>
-      </c>
-      <c r="X3">
-        <v>0.07076184092187615</v>
-      </c>
-      <c r="Y3">
-        <v>-0.002279931186702708</v>
-      </c>
-      <c r="Z3">
-        <v>1.336319015115338</v>
-      </c>
-      <c r="AA3">
-        <v>0.08255136984124596</v>
-      </c>
-      <c r="AB3">
-        <v>0.07073538933421071</v>
-      </c>
-      <c r="AC3">
-        <v>0.01181598050703525</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>1.224801691490527</v>
-      </c>
-      <c r="AF3">
-        <v>1.224801691490527</v>
-      </c>
-      <c r="AG3">
-        <v>-271.1751983085094</v>
-      </c>
-      <c r="AH3">
-        <v>0.0006417867187666765</v>
-      </c>
-      <c r="AI3">
-        <v>0.0008672852155149252</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.1657524983900859</v>
-      </c>
-      <c r="AK3">
-        <v>-0.2379095435597538</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>-2.553534957140659</v>
+      <c r="D4">
+        <v>-0.04019999999999999</v>
+      </c>
+      <c r="E4">
+        <v>-0.0375</v>
+      </c>
+      <c r="G4">
+        <v>0.08436445444319461</v>
+      </c>
+      <c r="H4">
+        <v>0.08436445444319461</v>
+      </c>
+      <c r="I4">
+        <v>0.07676900820232953</v>
+      </c>
+      <c r="J4">
+        <v>0.06518846850347662</v>
+      </c>
+      <c r="K4">
+        <v>85</v>
+      </c>
+      <c r="L4">
+        <v>0.06829503454925277</v>
+      </c>
+      <c r="M4">
+        <v>39.7</v>
+      </c>
+      <c r="N4">
+        <v>0.02795577776212943</v>
+      </c>
+      <c r="O4">
+        <v>0.4670588235294118</v>
+      </c>
+      <c r="P4">
+        <v>39.7</v>
+      </c>
+      <c r="Q4">
+        <v>0.02795577776212943</v>
+      </c>
+      <c r="R4">
+        <v>0.4670588235294118</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>270.5</v>
+      </c>
+      <c r="V4">
+        <v>0.1904795436941061</v>
+      </c>
+      <c r="W4">
+        <v>0.06024096385542169</v>
+      </c>
+      <c r="X4">
+        <v>0.1084429385406789</v>
+      </c>
+      <c r="Y4">
+        <v>-0.04820197468525719</v>
+      </c>
+      <c r="Z4">
+        <v>1.092416100768835</v>
+      </c>
+      <c r="AA4">
+        <v>0.07121293257765997</v>
+      </c>
+      <c r="AB4">
+        <v>0.1084135270011288</v>
+      </c>
+      <c r="AC4">
+        <v>-0.03720059442346885</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0.8564619569033876</v>
+      </c>
+      <c r="AF4">
+        <v>0.8564619569033876</v>
+      </c>
+      <c r="AG4">
+        <v>-269.6435380430966</v>
+      </c>
+      <c r="AH4">
+        <v>0.0006027362412806731</v>
+      </c>
+      <c r="AI4">
+        <v>0.0007781373993667814</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.2343796110149517</v>
+      </c>
+      <c r="AK4">
+        <v>-0.3248105030797133</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-2.73977867913488</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_insurance_life.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.005899999999999997</v>
+        <v>-0.0117</v>
       </c>
       <c r="E2">
-        <v>0.01235</v>
+        <v>-0.04285</v>
       </c>
       <c r="F2">
-        <v>0.0401</v>
+        <v>0.007079999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1056012271409055</v>
+        <v>0.1076290717289553</v>
       </c>
       <c r="H2">
-        <v>0.1056012271409055</v>
+        <v>0.1076290717289553</v>
       </c>
       <c r="I2">
-        <v>0.08782846574038765</v>
+        <v>0.09305132859020486</v>
       </c>
       <c r="J2">
-        <v>0.07256384678990965</v>
+        <v>0.07746816017452768</v>
       </c>
       <c r="K2">
-        <v>302.6</v>
+        <v>313</v>
       </c>
       <c r="L2">
-        <v>0.07252594492246485</v>
+        <v>0.07436622395400223</v>
       </c>
       <c r="M2">
-        <v>109.9</v>
+        <v>120.1</v>
       </c>
       <c r="N2">
-        <v>0.01729238128205935</v>
+        <v>0.02955143820280013</v>
       </c>
       <c r="O2">
-        <v>0.3631857237276933</v>
+        <v>0.3837060702875399</v>
       </c>
       <c r="P2">
-        <v>109.9</v>
+        <v>120.1</v>
       </c>
       <c r="Q2">
-        <v>0.01729238128205935</v>
+        <v>0.02955143820280013</v>
       </c>
       <c r="R2">
-        <v>0.3631857237276933</v>
+        <v>0.3837060702875399</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,55 +639,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>420.5</v>
+        <v>273.9</v>
       </c>
       <c r="V2">
-        <v>0.06616420681625075</v>
+        <v>0.06739499520188971</v>
       </c>
       <c r="W2">
-        <v>0.07372420106846109</v>
+        <v>0.08238466859816218</v>
       </c>
       <c r="X2">
-        <v>0.1084261854794475</v>
+        <v>0.09281737397919239</v>
       </c>
       <c r="Y2">
-        <v>-0.03470198441098644</v>
+        <v>-0.01043270538103021</v>
       </c>
       <c r="Z2">
-        <v>1.184501701196897</v>
+        <v>1.378113620706834</v>
       </c>
       <c r="AA2">
-        <v>0.08126128564177362</v>
+        <v>0.1007684564724793</v>
       </c>
       <c r="AB2">
-        <v>0.1084114472838926</v>
+        <v>0.09280609000766829</v>
       </c>
       <c r="AC2">
-        <v>-0.02715016164211895</v>
+        <v>0.007962366464810952</v>
       </c>
       <c r="AD2">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.8564619569033876</v>
+        <v>0.5263154834338217</v>
       </c>
       <c r="AF2">
-        <v>0.8634619569033876</v>
+        <v>0.5263154834338217</v>
       </c>
       <c r="AG2">
-        <v>-419.6365380430966</v>
+        <v>-273.3736845165661</v>
       </c>
       <c r="AH2">
-        <v>0.0001358442679525989</v>
+        <v>0.0001294868070476544</v>
       </c>
       <c r="AI2">
-        <v>0.0002484737232445098</v>
+        <v>0.000135350886359731</v>
       </c>
       <c r="AJ2">
-        <v>-0.0706963039771721</v>
+        <v>-0.07211643937468026</v>
       </c>
       <c r="AK2">
-        <v>-0.1373801995831695</v>
+        <v>-0.07562986064300926</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1.855690873712283e-05</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>-1.112450991318274</v>
+        <v>-0.6794441753715459</v>
       </c>
     </row>
     <row r="3">
@@ -719,49 +719,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0284</v>
+        <v>0.0159</v>
       </c>
       <c r="E3">
-        <v>0.0622</v>
+        <v>0.0693</v>
       </c>
       <c r="F3">
-        <v>0.0401</v>
+        <v>0.007079999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1146292311370701</v>
+        <v>0.115028332937464</v>
       </c>
       <c r="H3">
-        <v>0.1146292311370701</v>
+        <v>0.115028332937464</v>
       </c>
       <c r="I3">
-        <v>0.09252997233323086</v>
+        <v>0.1028807980726816</v>
       </c>
       <c r="J3">
-        <v>0.07432455511152099</v>
+        <v>0.08326829764853586</v>
       </c>
       <c r="K3">
-        <v>217.6</v>
+        <v>245.5</v>
       </c>
       <c r="L3">
-        <v>0.07432455511152099</v>
+        <v>0.08330222931016933</v>
       </c>
       <c r="M3">
-        <v>70.2</v>
+        <v>94</v>
       </c>
       <c r="N3">
-        <v>0.01422405932770044</v>
+        <v>0.03066884176182708</v>
       </c>
       <c r="O3">
-        <v>0.3226102941176471</v>
+        <v>0.3828920570264766</v>
       </c>
       <c r="P3">
-        <v>70.2</v>
+        <v>94</v>
       </c>
       <c r="Q3">
-        <v>0.01422405932770044</v>
+        <v>0.03066884176182708</v>
       </c>
       <c r="R3">
-        <v>0.3226102941176471</v>
+        <v>0.3828920570264766</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>150</v>
+        <v>95.2</v>
       </c>
       <c r="V3">
-        <v>0.03039328916175308</v>
+        <v>0.03106035889070147</v>
       </c>
       <c r="W3">
-        <v>0.08720743828150049</v>
+        <v>0.1033945417789757</v>
       </c>
       <c r="X3">
-        <v>0.1084094324182162</v>
+        <v>0.09280599406091694</v>
       </c>
       <c r="Y3">
-        <v>-0.0212019941367157</v>
+        <v>0.0105885477180588</v>
       </c>
       <c r="Z3">
-        <v>1.228525869665562</v>
+        <v>1.324892432005474</v>
       </c>
       <c r="AA3">
-        <v>0.09130963870588729</v>
+        <v>0.1103215373805243</v>
       </c>
       <c r="AB3">
-        <v>0.1084093675666564</v>
+        <v>0.09280599406091694</v>
       </c>
       <c r="AC3">
-        <v>-0.01709972886076906</v>
+        <v>0.01751554331960739</v>
       </c>
       <c r="AD3">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-149.993</v>
+        <v>-95.2</v>
       </c>
       <c r="AH3">
-        <v>1.418351482491363e-06</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>2.948104516201308e-06</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0313444884518381</v>
+        <v>-0.03205603070913866</v>
       </c>
       <c r="AK3">
-        <v>-0.06743055564921346</v>
+        <v>-0.03646531581568162</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>2.510760401721664e-05</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.5379949784791965</v>
+        <v>-0.3067010309278351</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.04019999999999999</v>
+        <v>-0.0393</v>
       </c>
       <c r="E4">
-        <v>-0.0375</v>
+        <v>-0.155</v>
       </c>
       <c r="G4">
-        <v>0.08436445444319461</v>
+        <v>0.0903471231573942</v>
       </c>
       <c r="H4">
-        <v>0.08436445444319461</v>
+        <v>0.0903471231573942</v>
       </c>
       <c r="I4">
-        <v>0.07676900820232953</v>
+        <v>0.07009330868862992</v>
       </c>
       <c r="J4">
-        <v>0.06518846850347662</v>
+        <v>0.05997857806773903</v>
       </c>
       <c r="K4">
-        <v>85</v>
+        <v>67.5</v>
       </c>
       <c r="L4">
-        <v>0.06829503454925277</v>
+        <v>0.05349500713266762</v>
       </c>
       <c r="M4">
-        <v>39.7</v>
+        <v>26.1</v>
       </c>
       <c r="N4">
-        <v>0.02795577776212943</v>
+        <v>0.02612351116004404</v>
       </c>
       <c r="O4">
-        <v>0.4670588235294118</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="P4">
-        <v>39.7</v>
+        <v>26.1</v>
       </c>
       <c r="Q4">
-        <v>0.02795577776212943</v>
+        <v>0.02612351116004404</v>
       </c>
       <c r="R4">
-        <v>0.4670588235294118</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,55 +898,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>270.5</v>
+        <v>178.7</v>
       </c>
       <c r="V4">
-        <v>0.1904795436941061</v>
+        <v>0.1788609748773896</v>
       </c>
       <c r="W4">
-        <v>0.06024096385542169</v>
+        <v>0.06137479541734861</v>
       </c>
       <c r="X4">
-        <v>0.1084429385406789</v>
+        <v>0.09282875389746784</v>
       </c>
       <c r="Y4">
-        <v>-0.04820197468525719</v>
+        <v>-0.03145395848011923</v>
       </c>
       <c r="Z4">
-        <v>1.092416100768835</v>
+        <v>1.520799233710021</v>
       </c>
       <c r="AA4">
-        <v>0.07121293257765997</v>
+        <v>0.09121537556443417</v>
       </c>
       <c r="AB4">
-        <v>0.1084135270011288</v>
+        <v>0.09280618595441965</v>
       </c>
       <c r="AC4">
-        <v>-0.03720059442346885</v>
+        <v>-0.001590810389985486</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0.8564619569033876</v>
+        <v>0.5263154834338217</v>
       </c>
       <c r="AF4">
-        <v>0.8564619569033876</v>
+        <v>0.5263154834338217</v>
       </c>
       <c r="AG4">
-        <v>-269.6435380430966</v>
+        <v>-178.1736845165662</v>
       </c>
       <c r="AH4">
-        <v>0.0006027362412806731</v>
+        <v>0.0005265122329030403</v>
       </c>
       <c r="AI4">
-        <v>0.0007781373993667814</v>
+        <v>0.0004450395501462138</v>
       </c>
       <c r="AJ4">
-        <v>-0.2343796110149517</v>
+        <v>-0.2170398014487351</v>
       </c>
       <c r="AK4">
-        <v>-0.3248105030797133</v>
+        <v>-0.1774768543952032</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-2.73977867913488</v>
+        <v>-1.93774466842017</v>
       </c>
     </row>
   </sheetData>
